--- a/docs/02. Source Systems/04. Payment System/Payment_System_Data_Dictionary.xlsx
+++ b/docs/02. Source Systems/04. Payment System/Payment_System_Data_Dictionary.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\consumer-finance-analytics-platform\docs\02. Source Systems\04. Payment System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A76208-3DA4-4FD8-BDFE-3459290BB9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4306613-3F5C-4894-90EF-68E3F081FB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="loan_contract" sheetId="1" r:id="rId1"/>
+    <sheet name="contract" sheetId="1" r:id="rId1"/>
     <sheet name="repayment_schedule" sheetId="2" r:id="rId2"/>
     <sheet name="payment_transaction" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="145">
   <si>
     <t>Column</t>
   </si>
@@ -63,6 +63,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>gen_random_uuid()</t>
   </si>
   <si>
@@ -78,10 +81,7 @@
     <t>VARCHAR(30)</t>
   </si>
   <si>
-    <t>LN202607000123</t>
-  </si>
-  <si>
-    <t>Số hợp đồng vay do Payment System sinh để quản lý và tra cứu nghiệp vụ.</t>
+    <t>100012345678</t>
   </si>
   <si>
     <t>payment_reference_id</t>
@@ -454,27 +454,22 @@
   </si>
   <si>
     <t>Thời điểm bản ghi giao dịch được cập nhật gần nhất; phục vụ tải dữ liệu tăng dần và CDC.</t>
+  </si>
+  <si>
+    <t>Số hợp đồng do Payment System sinh để quản lý và tra cứu nghiệp vụ.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -486,7 +481,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -517,23 +513,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -546,9 +548,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -556,74 +558,173 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -632,62 +733,136 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-                <a:satMod val="150000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-                <a:satMod val="130000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -695,348 +870,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="68" customWidth="1"/>
+    <col min="1" max="1" width="23.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.8984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="74.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.35" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="27.6">
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="J2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="27.6">
+      <c r="J3" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="27.6">
+    <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="27.6">
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="27.6">
+    <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="H9" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="27.6">
+    <row r="10" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="H10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="27.6">
+    <row r="12" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="27.6">
+    <row r="13" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2" t="s">
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="27.6">
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2"/>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="G14" s="1" t="s">
         <v>60</v>
       </c>
@@ -1046,23 +1327,29 @@
       <c r="I14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="27.6">
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>65</v>
       </c>
@@ -1072,130 +1359,149 @@
       <c r="I15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2"/>
+      <c r="C16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="G16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="27.6">
+    <row r="17" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2"/>
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="G17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="1"/>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="I17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="2" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J2 A4:J17 A3:I3" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="68" customWidth="1"/>
+    <col min="1" max="1" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="84.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.35" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="27.6">
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
@@ -1205,43 +1511,43 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="27.6">
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2"/>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="27.6">
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
         <v>83</v>
@@ -1253,19 +1559,19 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
@@ -1275,19 +1581,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
         <v>61</v>
@@ -1299,19 +1605,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
         <v>61</v>
@@ -1323,19 +1629,19 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="27.6">
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
         <v>61</v>
@@ -1347,19 +1653,19 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="2"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
         <v>100</v>
       </c>
@@ -1373,19 +1679,19 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
@@ -1395,19 +1701,19 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
         <v>71</v>
       </c>
@@ -1419,19 +1725,19 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="27.6">
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
         <v>71</v>
       </c>
@@ -1445,98 +1751,101 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J12" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="29.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="68" customWidth="1"/>
+    <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="70.59765625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.35" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="27.6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="1"/>
@@ -1544,71 +1853,71 @@
       <c r="I3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="27.6">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2"/>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="27.6">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="2"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
         <v>119</v>
@@ -1616,23 +1925,23 @@
       <c r="I6" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
         <v>36</v>
@@ -1640,23 +1949,23 @@
       <c r="I7" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="27.6">
+    <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
         <v>60</v>
       </c>
@@ -1666,23 +1975,23 @@
       <c r="I8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="2"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
         <v>60</v>
       </c>
@@ -1692,23 +2001,23 @@
       <c r="I9" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="27.6">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
         <v>128</v>
@@ -1716,23 +2025,23 @@
       <c r="I10" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="27.6">
+    <row r="11" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
         <v>100</v>
       </c>
@@ -1742,45 +2051,45 @@
       <c r="I11" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="27.6">
+    <row r="12" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
         <v>71</v>
       </c>
@@ -1788,23 +2097,23 @@
       <c r="I13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
         <v>71</v>
       </c>
@@ -1812,23 +2121,23 @@
       <c r="I14" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="27.6">
+    <row r="15" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
         <v>71</v>
       </c>
@@ -1836,11 +2145,14 @@
       <c r="I15" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="2" t="s">
         <v>143</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J15" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/02. Source Systems/04. Payment System/Payment_System_Data_Dictionary.xlsx
+++ b/docs/02. Source Systems/04. Payment System/Payment_System_Data_Dictionary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kienl\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\consumer-finance-analytics-platform\docs\02. Source Systems\04. Payment System\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F614A27A-CF3E-4E42-AB16-22CCC21DDD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
